--- a/スケジュール結果.xlsx
+++ b/スケジュール結果.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,10 +508,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -520,25 +520,25 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>430</v>
+        <v>30</v>
       </c>
       <c r="I2" t="n">
-        <v>651</v>
+        <v>118</v>
       </c>
       <c r="J2" t="n">
         <v>30</v>
       </c>
       <c r="K2" t="n">
-        <v>221</v>
+        <v>88</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -547,18 +547,18 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -573,19 +573,19 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H3" t="n">
-        <v>30</v>
+        <v>148</v>
       </c>
       <c r="I3" t="n">
-        <v>118</v>
+        <v>365</v>
       </c>
       <c r="J3" t="n">
         <v>30</v>
       </c>
       <c r="K3" t="n">
-        <v>88</v>
+        <v>217</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -594,18 +594,18 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -614,25 +614,25 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>651</v>
+        <v>365</v>
       </c>
       <c r="H4" t="n">
-        <v>681</v>
+        <v>395</v>
       </c>
       <c r="I4" t="n">
-        <v>822</v>
+        <v>668</v>
       </c>
       <c r="J4" t="n">
         <v>30</v>
       </c>
       <c r="K4" t="n">
-        <v>141</v>
+        <v>273</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -641,18 +641,18 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -661,25 +661,25 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>822</v>
+        <v>1440</v>
       </c>
       <c r="H5" t="n">
-        <v>852</v>
+        <v>1470</v>
       </c>
       <c r="I5" t="n">
-        <v>1314</v>
+        <v>1719</v>
       </c>
       <c r="J5" t="n">
         <v>30</v>
       </c>
       <c r="K5" t="n">
-        <v>462</v>
+        <v>249</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -688,18 +688,18 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>440</v>
+        <v>180</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -708,25 +708,25 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1314</v>
+        <v>1719</v>
       </c>
       <c r="H6" t="n">
-        <v>1344</v>
+        <v>1749</v>
       </c>
       <c r="I6" t="n">
-        <v>1617</v>
+        <v>2121</v>
       </c>
       <c r="J6" t="n">
         <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>273</v>
+        <v>372</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
@@ -735,18 +735,18 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -761,19 +761,19 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1617</v>
+        <v>2880</v>
       </c>
       <c r="H7" t="n">
-        <v>1647</v>
+        <v>2910</v>
       </c>
       <c r="I7" t="n">
-        <v>1864</v>
+        <v>3372</v>
       </c>
       <c r="J7" t="n">
         <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>217</v>
+        <v>462</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -782,18 +782,18 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>140</v>
+        <v>440</v>
       </c>
       <c r="O7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -802,25 +802,25 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1864</v>
+        <v>4320</v>
       </c>
       <c r="H8" t="n">
-        <v>1894</v>
+        <v>4350</v>
       </c>
       <c r="I8" t="n">
-        <v>2266</v>
+        <v>4571</v>
       </c>
       <c r="J8" t="n">
         <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>372</v>
+        <v>221</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -829,18 +829,18 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -849,25 +849,25 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2266</v>
+        <v>4571</v>
       </c>
       <c r="H9" t="n">
-        <v>2296</v>
+        <v>4601</v>
       </c>
       <c r="I9" t="n">
-        <v>2668</v>
+        <v>5314</v>
       </c>
       <c r="J9" t="n">
         <v>30</v>
       </c>
       <c r="K9" t="n">
-        <v>372</v>
+        <v>713</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -876,18 +876,18 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>240</v>
+        <v>460</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -896,25 +896,25 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2668</v>
+        <v>5760</v>
       </c>
       <c r="H10" t="n">
-        <v>2698</v>
+        <v>5790</v>
       </c>
       <c r="I10" t="n">
-        <v>3411</v>
+        <v>5931</v>
       </c>
       <c r="J10" t="n">
         <v>30</v>
       </c>
       <c r="K10" t="n">
-        <v>713</v>
+        <v>141</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
@@ -923,18 +923,18 @@
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>460</v>
+        <v>160</v>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -949,19 +949,19 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3411</v>
+        <v>6000</v>
       </c>
       <c r="H11" t="n">
-        <v>3441</v>
+        <v>6030</v>
       </c>
       <c r="I11" t="n">
-        <v>3690</v>
+        <v>6402</v>
       </c>
       <c r="J11" t="n">
         <v>30</v>
       </c>
       <c r="K11" t="n">
-        <v>249</v>
+        <v>372</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -970,45 +970,45 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>401</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>430</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>460</v>
+        <v>81</v>
       </c>
       <c r="I12" t="n">
-        <v>940</v>
+        <v>381</v>
       </c>
       <c r="J12" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="K12" t="n">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -1017,10 +1017,10 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1031,31 +1031,31 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>431</v>
+        <v>4321</v>
       </c>
       <c r="G13" t="n">
-        <v>460</v>
+        <v>4350</v>
       </c>
       <c r="H13" t="n">
-        <v>540</v>
+        <v>4380</v>
       </c>
       <c r="I13" t="n">
-        <v>1340</v>
+        <v>4860</v>
       </c>
       <c r="J13" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="K13" t="n">
-        <v>800</v>
+        <v>480</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -1078,31 +1078,31 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>660</v>
+        <v>4351</v>
       </c>
       <c r="G14" t="n">
-        <v>1340</v>
+        <v>4351</v>
       </c>
       <c r="H14" t="n">
-        <v>1380</v>
+        <v>4431</v>
       </c>
       <c r="I14" t="n">
-        <v>2020</v>
+        <v>5231</v>
       </c>
       <c r="J14" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K14" t="n">
-        <v>640</v>
+        <v>800</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -1119,37 +1119,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>4551</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4601</v>
       </c>
       <c r="H15" t="n">
-        <v>81</v>
+        <v>4641</v>
       </c>
       <c r="I15" t="n">
-        <v>381</v>
+        <v>5281</v>
       </c>
       <c r="J15" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K15" t="n">
-        <v>300</v>
+        <v>640</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -1158,10 +1158,10 @@
         <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1178,19 +1178,19 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1315</v>
+        <v>366</v>
       </c>
       <c r="G16" t="n">
-        <v>1315</v>
+        <v>366</v>
       </c>
       <c r="H16" t="n">
-        <v>1395</v>
+        <v>446</v>
       </c>
       <c r="I16" t="n">
-        <v>3215</v>
+        <v>2266</v>
       </c>
       <c r="J16" t="n">
         <v>80</v>
@@ -1222,22 +1222,22 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1365</v>
+        <v>416</v>
       </c>
       <c r="G17" t="n">
-        <v>3215</v>
+        <v>446</v>
       </c>
       <c r="H17" t="n">
-        <v>3245</v>
+        <v>476</v>
       </c>
       <c r="I17" t="n">
-        <v>5065</v>
+        <v>2296</v>
       </c>
       <c r="J17" t="n">
         <v>30</v>
@@ -1269,22 +1269,22 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>4225</v>
+        <v>1456</v>
       </c>
       <c r="G18" t="n">
-        <v>4225</v>
+        <v>2880</v>
       </c>
       <c r="H18" t="n">
-        <v>4285</v>
+        <v>2940</v>
       </c>
       <c r="I18" t="n">
-        <v>5065</v>
+        <v>3720</v>
       </c>
       <c r="J18" t="n">
         <v>60</v>
@@ -1307,37 +1307,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>1865</v>
+        <v>6001</v>
       </c>
       <c r="G19" t="n">
-        <v>2020</v>
+        <v>6001</v>
       </c>
       <c r="H19" t="n">
-        <v>2090</v>
+        <v>6031</v>
       </c>
       <c r="I19" t="n">
-        <v>3770</v>
+        <v>6991</v>
       </c>
       <c r="J19" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="K19" t="n">
-        <v>1680</v>
+        <v>960</v>
       </c>
       <c r="L19" t="b">
         <v>1</v>
@@ -1349,42 +1349,42 @@
         <v>240</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>2267</v>
+        <v>1720</v>
       </c>
       <c r="G20" t="n">
-        <v>5065</v>
+        <v>5760</v>
       </c>
       <c r="H20" t="n">
-        <v>5095</v>
+        <v>5830</v>
       </c>
       <c r="I20" t="n">
-        <v>6055</v>
+        <v>7510</v>
       </c>
       <c r="J20" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="K20" t="n">
-        <v>960</v>
+        <v>1680</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
@@ -1396,42 +1396,42 @@
         <v>240</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>652</v>
+        <v>1441</v>
       </c>
       <c r="G21" t="n">
-        <v>1395</v>
+        <v>1441</v>
       </c>
       <c r="H21" t="n">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="I21" t="n">
-        <v>1955</v>
+        <v>2011</v>
       </c>
       <c r="J21" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="K21" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="L21" t="b">
         <v>1</v>
@@ -1440,10 +1440,10 @@
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="O21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -1454,7 +1454,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>4</v>
@@ -1463,22 +1463,22 @@
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>3412</v>
+        <v>1442</v>
       </c>
       <c r="G22" t="n">
-        <v>6055</v>
+        <v>2880</v>
       </c>
       <c r="H22" t="n">
-        <v>6085</v>
+        <v>2960</v>
       </c>
       <c r="I22" t="n">
-        <v>6625</v>
+        <v>3860</v>
       </c>
       <c r="J22" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="K22" t="n">
-        <v>540</v>
+        <v>900</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>6056</v>
+        <v>3100</v>
       </c>
       <c r="G23" t="n">
-        <v>6625</v>
+        <v>7510</v>
       </c>
       <c r="H23" t="n">
-        <v>6705</v>
+        <v>7550</v>
       </c>
       <c r="I23" t="n">
-        <v>7605</v>
+        <v>8270</v>
       </c>
       <c r="J23" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K23" t="n">
-        <v>900</v>
+        <v>720</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
@@ -1542,13 +1542,13 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
         <v>4</v>
@@ -1557,22 +1557,22 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>6845</v>
+        <v>2881</v>
       </c>
       <c r="G24" t="n">
-        <v>7605</v>
+        <v>5790</v>
       </c>
       <c r="H24" t="n">
-        <v>7645</v>
+        <v>5870</v>
       </c>
       <c r="I24" t="n">
-        <v>8365</v>
+        <v>8950</v>
       </c>
       <c r="J24" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K24" t="n">
-        <v>720</v>
+        <v>3080</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
@@ -1581,10 +1581,10 @@
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>180</v>
+        <v>440</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -1595,28 +1595,28 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>823</v>
+        <v>5840</v>
       </c>
       <c r="G25" t="n">
-        <v>2090</v>
+        <v>7200</v>
       </c>
       <c r="H25" t="n">
-        <v>2170</v>
+        <v>7230</v>
       </c>
       <c r="I25" t="n">
-        <v>5250</v>
+        <v>10310</v>
       </c>
       <c r="J25" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
         <v>3080</v>
@@ -1642,31 +1642,31 @@
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>2140</v>
+        <v>8930</v>
       </c>
       <c r="G26" t="n">
-        <v>5065</v>
+        <v>8950</v>
       </c>
       <c r="H26" t="n">
-        <v>5095</v>
+        <v>9010</v>
       </c>
       <c r="I26" t="n">
-        <v>8175</v>
+        <v>10330</v>
       </c>
       <c r="J26" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K26" t="n">
-        <v>3080</v>
+        <v>1320</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -1683,37 +1683,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>6795</v>
+        <v>5761</v>
       </c>
       <c r="G27" t="n">
-        <v>8365</v>
+        <v>10320</v>
       </c>
       <c r="H27" t="n">
-        <v>8425</v>
+        <v>10400</v>
       </c>
       <c r="I27" t="n">
-        <v>9745</v>
+        <v>10880</v>
       </c>
       <c r="J27" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K27" t="n">
-        <v>1320</v>
+        <v>480</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
@@ -1722,10 +1722,10 @@
         <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>440</v>
+        <v>160</v>
       </c>
       <c r="O27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1739,22 +1739,22 @@
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>1618</v>
+        <v>119</v>
       </c>
       <c r="G28" t="n">
-        <v>5250</v>
+        <v>2910</v>
       </c>
       <c r="H28" t="n">
-        <v>5280</v>
+        <v>2940</v>
       </c>
       <c r="I28" t="n">
-        <v>5840</v>
+        <v>3500</v>
       </c>
       <c r="J28" t="n">
         <v>30</v>
@@ -1789,19 +1789,19 @@
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>2669</v>
+        <v>4572</v>
       </c>
       <c r="G29" t="n">
-        <v>5840</v>
+        <v>8640</v>
       </c>
       <c r="H29" t="n">
-        <v>5910</v>
+        <v>8710</v>
       </c>
       <c r="I29" t="n">
-        <v>9130</v>
+        <v>11930</v>
       </c>
       <c r="J29" t="n">
         <v>70</v>
@@ -1821,87 +1821,6 @@
       <c r="O29" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>強制停止</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="n">
-        <v>240</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>400</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>強制停止</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>強制停止</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="n">
-        <v>400</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="n">
-        <v>500</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1941,7 +1860,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9745</v>
+        <v>11930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/スケジュール結果.xlsx
+++ b/スケジュール結果.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スケジュール" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="評価" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="稼働設定" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -508,10 +509,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -520,25 +521,25 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H2" t="n">
-        <v>30</v>
+        <v>270</v>
       </c>
       <c r="I2" t="n">
-        <v>118</v>
+        <v>491</v>
       </c>
       <c r="J2" t="n">
         <v>30</v>
       </c>
       <c r="K2" t="n">
-        <v>88</v>
+        <v>221</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -547,18 +548,18 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -567,25 +568,25 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>118</v>
+        <v>1440</v>
       </c>
       <c r="H3" t="n">
-        <v>148</v>
+        <v>1470</v>
       </c>
       <c r="I3" t="n">
-        <v>365</v>
+        <v>1558</v>
       </c>
       <c r="J3" t="n">
         <v>30</v>
       </c>
       <c r="K3" t="n">
-        <v>217</v>
+        <v>88</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -594,10 +595,10 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -614,19 +615,19 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>365</v>
+        <v>1558</v>
       </c>
       <c r="H4" t="n">
-        <v>395</v>
+        <v>1588</v>
       </c>
       <c r="I4" t="n">
-        <v>668</v>
+        <v>1861</v>
       </c>
       <c r="J4" t="n">
         <v>30</v>
@@ -649,10 +650,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -661,25 +662,25 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1440</v>
+        <v>1861</v>
       </c>
       <c r="H5" t="n">
-        <v>1470</v>
+        <v>1891</v>
       </c>
       <c r="I5" t="n">
-        <v>1719</v>
+        <v>2263</v>
       </c>
       <c r="J5" t="n">
         <v>30</v>
       </c>
       <c r="K5" t="n">
-        <v>249</v>
+        <v>372</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -688,10 +689,10 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -708,19 +709,19 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1719</v>
+        <v>3200</v>
       </c>
       <c r="H6" t="n">
-        <v>1749</v>
+        <v>3230</v>
       </c>
       <c r="I6" t="n">
-        <v>2121</v>
+        <v>3602</v>
       </c>
       <c r="J6" t="n">
         <v>30</v>
@@ -743,10 +744,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -755,25 +756,25 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2880</v>
+        <v>4320</v>
       </c>
       <c r="H7" t="n">
-        <v>2910</v>
+        <v>4350</v>
       </c>
       <c r="I7" t="n">
-        <v>3372</v>
+        <v>4599</v>
       </c>
       <c r="J7" t="n">
         <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>462</v>
+        <v>249</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -782,18 +783,18 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>440</v>
+        <v>180</v>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -808,19 +809,19 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4320</v>
+        <v>4599</v>
       </c>
       <c r="H8" t="n">
-        <v>4350</v>
+        <v>4629</v>
       </c>
       <c r="I8" t="n">
-        <v>4571</v>
+        <v>4770</v>
       </c>
       <c r="J8" t="n">
         <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>221</v>
+        <v>141</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -832,15 +833,15 @@
         <v>160</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -849,25 +850,25 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>4571</v>
+        <v>4770</v>
       </c>
       <c r="H9" t="n">
-        <v>4601</v>
+        <v>4800</v>
       </c>
       <c r="I9" t="n">
-        <v>5314</v>
+        <v>5262</v>
       </c>
       <c r="J9" t="n">
         <v>30</v>
       </c>
       <c r="K9" t="n">
-        <v>713</v>
+        <v>462</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -876,18 +877,18 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -896,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -908,13 +909,13 @@
         <v>5790</v>
       </c>
       <c r="I10" t="n">
-        <v>5931</v>
+        <v>6007</v>
       </c>
       <c r="J10" t="n">
         <v>30</v>
       </c>
       <c r="K10" t="n">
-        <v>141</v>
+        <v>217</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
@@ -923,18 +924,18 @@
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -943,25 +944,25 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>6000</v>
+        <v>6007</v>
       </c>
       <c r="H11" t="n">
-        <v>6030</v>
+        <v>6037</v>
       </c>
       <c r="I11" t="n">
-        <v>6402</v>
+        <v>6750</v>
       </c>
       <c r="J11" t="n">
         <v>30</v>
       </c>
       <c r="K11" t="n">
-        <v>372</v>
+        <v>713</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -970,45 +971,45 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>240</v>
+        <v>460</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>241</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>241</v>
       </c>
       <c r="H12" t="n">
-        <v>81</v>
+        <v>271</v>
       </c>
       <c r="I12" t="n">
-        <v>381</v>
+        <v>751</v>
       </c>
       <c r="J12" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="K12" t="n">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -1017,10 +1018,10 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1031,31 +1032,31 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>4321</v>
+        <v>242</v>
       </c>
       <c r="G13" t="n">
-        <v>4350</v>
+        <v>270</v>
       </c>
       <c r="H13" t="n">
-        <v>4380</v>
+        <v>350</v>
       </c>
       <c r="I13" t="n">
-        <v>4860</v>
+        <v>1150</v>
       </c>
       <c r="J13" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="K13" t="n">
-        <v>480</v>
+        <v>800</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -1078,31 +1079,31 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>4351</v>
+        <v>470</v>
       </c>
       <c r="G14" t="n">
-        <v>4351</v>
+        <v>1440</v>
       </c>
       <c r="H14" t="n">
-        <v>4431</v>
+        <v>1480</v>
       </c>
       <c r="I14" t="n">
-        <v>5231</v>
+        <v>2120</v>
       </c>
       <c r="J14" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K14" t="n">
-        <v>800</v>
+        <v>640</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -1119,37 +1120,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>4551</v>
+        <v>1441</v>
       </c>
       <c r="G15" t="n">
-        <v>4601</v>
+        <v>2880</v>
       </c>
       <c r="H15" t="n">
-        <v>4641</v>
+        <v>2960</v>
       </c>
       <c r="I15" t="n">
-        <v>5281</v>
+        <v>3260</v>
       </c>
       <c r="J15" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K15" t="n">
-        <v>640</v>
+        <v>300</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -1158,10 +1159,10 @@
         <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1175,22 +1176,22 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>366</v>
+        <v>1559</v>
       </c>
       <c r="G16" t="n">
-        <v>366</v>
+        <v>1680</v>
       </c>
       <c r="H16" t="n">
-        <v>446</v>
+        <v>1760</v>
       </c>
       <c r="I16" t="n">
-        <v>2266</v>
+        <v>3580</v>
       </c>
       <c r="J16" t="n">
         <v>80</v>
@@ -1222,22 +1223,22 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>416</v>
+        <v>1730</v>
       </c>
       <c r="G17" t="n">
-        <v>446</v>
+        <v>1800</v>
       </c>
       <c r="H17" t="n">
-        <v>476</v>
+        <v>1830</v>
       </c>
       <c r="I17" t="n">
-        <v>2296</v>
+        <v>3650</v>
       </c>
       <c r="J17" t="n">
         <v>30</v>
@@ -1269,22 +1270,22 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>1456</v>
+        <v>2810</v>
       </c>
       <c r="G18" t="n">
-        <v>2880</v>
+        <v>4320</v>
       </c>
       <c r="H18" t="n">
-        <v>2940</v>
+        <v>4380</v>
       </c>
       <c r="I18" t="n">
-        <v>3720</v>
+        <v>5160</v>
       </c>
       <c r="J18" t="n">
         <v>60</v>
@@ -1319,19 +1320,19 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>6001</v>
+        <v>1862</v>
       </c>
       <c r="G19" t="n">
-        <v>6001</v>
+        <v>4380</v>
       </c>
       <c r="H19" t="n">
-        <v>6031</v>
+        <v>4410</v>
       </c>
       <c r="I19" t="n">
-        <v>6991</v>
+        <v>5370</v>
       </c>
       <c r="J19" t="n">
         <v>30</v>
@@ -1363,22 +1364,22 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>1720</v>
+        <v>3201</v>
       </c>
       <c r="G20" t="n">
-        <v>5760</v>
+        <v>5790</v>
       </c>
       <c r="H20" t="n">
-        <v>5830</v>
+        <v>5860</v>
       </c>
       <c r="I20" t="n">
-        <v>7510</v>
+        <v>7540</v>
       </c>
       <c r="J20" t="n">
         <v>70</v>
@@ -1416,16 +1417,16 @@
         <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>1441</v>
+        <v>4321</v>
       </c>
       <c r="G21" t="n">
-        <v>1441</v>
+        <v>7540</v>
       </c>
       <c r="H21" t="n">
-        <v>1471</v>
+        <v>7570</v>
       </c>
       <c r="I21" t="n">
-        <v>2011</v>
+        <v>8110</v>
       </c>
       <c r="J21" t="n">
         <v>30</v>
@@ -1457,22 +1458,22 @@
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>1442</v>
+        <v>7541</v>
       </c>
       <c r="G22" t="n">
-        <v>2880</v>
+        <v>7541</v>
       </c>
       <c r="H22" t="n">
-        <v>2960</v>
+        <v>7621</v>
       </c>
       <c r="I22" t="n">
-        <v>3860</v>
+        <v>8521</v>
       </c>
       <c r="J22" t="n">
         <v>80</v>
@@ -1495,37 +1496,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>3100</v>
+        <v>4600</v>
       </c>
       <c r="G23" t="n">
-        <v>7510</v>
+        <v>4629</v>
       </c>
       <c r="H23" t="n">
-        <v>7550</v>
+        <v>4709</v>
       </c>
       <c r="I23" t="n">
-        <v>8270</v>
+        <v>5189</v>
       </c>
       <c r="J23" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K23" t="n">
-        <v>720</v>
+        <v>480</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
@@ -1534,21 +1535,21 @@
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="O23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
         <v>4</v>
@@ -1557,22 +1558,22 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>2881</v>
+        <v>7761</v>
       </c>
       <c r="G24" t="n">
-        <v>5790</v>
+        <v>8640</v>
       </c>
       <c r="H24" t="n">
-        <v>5870</v>
+        <v>8680</v>
       </c>
       <c r="I24" t="n">
-        <v>8950</v>
+        <v>9400</v>
       </c>
       <c r="J24" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K24" t="n">
-        <v>3080</v>
+        <v>720</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
@@ -1581,21 +1582,21 @@
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>440</v>
+        <v>180</v>
       </c>
       <c r="O24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
         <v>3</v>
@@ -1604,22 +1605,22 @@
         <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>5840</v>
+        <v>5761</v>
       </c>
       <c r="G25" t="n">
-        <v>7200</v>
+        <v>5860</v>
       </c>
       <c r="H25" t="n">
-        <v>7230</v>
+        <v>5890</v>
       </c>
       <c r="I25" t="n">
-        <v>10310</v>
+        <v>6450</v>
       </c>
       <c r="J25" t="n">
         <v>30</v>
       </c>
       <c r="K25" t="n">
-        <v>3080</v>
+        <v>560</v>
       </c>
       <c r="L25" t="b">
         <v>1</v>
@@ -1628,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>440</v>
+        <v>140</v>
       </c>
       <c r="O25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -1642,31 +1643,31 @@
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>8930</v>
+        <v>4771</v>
       </c>
       <c r="G26" t="n">
-        <v>8950</v>
+        <v>5760</v>
       </c>
       <c r="H26" t="n">
-        <v>9010</v>
+        <v>5840</v>
       </c>
       <c r="I26" t="n">
-        <v>10330</v>
+        <v>8920</v>
       </c>
       <c r="J26" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K26" t="n">
-        <v>1320</v>
+        <v>3080</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -1683,37 +1684,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>5761</v>
+        <v>5810</v>
       </c>
       <c r="G27" t="n">
-        <v>10320</v>
+        <v>8680</v>
       </c>
       <c r="H27" t="n">
-        <v>10400</v>
+        <v>8710</v>
       </c>
       <c r="I27" t="n">
-        <v>10880</v>
+        <v>11790</v>
       </c>
       <c r="J27" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="K27" t="n">
-        <v>480</v>
+        <v>3080</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
@@ -1722,45 +1723,45 @@
         <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>160</v>
+        <v>440</v>
       </c>
       <c r="O27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
         <v>4</v>
       </c>
-      <c r="C28" t="n">
-        <v>2</v>
-      </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>119</v>
+        <v>10410</v>
       </c>
       <c r="G28" t="n">
-        <v>2910</v>
+        <v>10410</v>
       </c>
       <c r="H28" t="n">
-        <v>2940</v>
+        <v>10470</v>
       </c>
       <c r="I28" t="n">
-        <v>3500</v>
+        <v>11790</v>
       </c>
       <c r="J28" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K28" t="n">
-        <v>560</v>
+        <v>1320</v>
       </c>
       <c r="L28" t="b">
         <v>1</v>
@@ -1769,10 +1770,10 @@
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>140</v>
+        <v>440</v>
       </c>
       <c r="O28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -1792,16 +1793,16 @@
         <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>4572</v>
+        <v>6008</v>
       </c>
       <c r="G29" t="n">
-        <v>8640</v>
+        <v>8920</v>
       </c>
       <c r="H29" t="n">
-        <v>8710</v>
+        <v>8990</v>
       </c>
       <c r="I29" t="n">
-        <v>11930</v>
+        <v>12210</v>
       </c>
       <c r="J29" t="n">
         <v>70</v>
@@ -1860,13 +1861,465 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11930</v>
+        <v>12210</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>分</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>480</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>machine</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120</v>
+      </c>
+      <c r="B3" t="n">
+        <v>180</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>machine</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2900</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>machine</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>worker</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>worker</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>180</v>
+      </c>
+      <c r="B7" t="n">
+        <v>240</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>480</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1440</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1620</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2880</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3060</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3120</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3360</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4320</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4560</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4800</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5760</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5940</v>
+      </c>
+      <c r="B15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6240</v>
+      </c>
+      <c r="B16" t="n">
+        <v>7200</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7380</v>
+      </c>
+      <c r="B17" t="n">
+        <v>7440</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7680</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8640</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8820</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8880</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9120</v>
+      </c>
+      <c r="B20" t="n">
+        <v>10080</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>10260</v>
+      </c>
+      <c r="B21" t="n">
+        <v>10320</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>10560</v>
+      </c>
+      <c r="B22" t="n">
+        <v>11520</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>11700</v>
+      </c>
+      <c r="B23" t="n">
+        <v>11760</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>12000</v>
+      </c>
+      <c r="B24" t="n">
+        <v>12960</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>13140</v>
+      </c>
+      <c r="B25" t="n">
+        <v>13200</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>13440</v>
+      </c>
+      <c r="B26" t="n">
+        <v>14400</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>14580</v>
+      </c>
+      <c r="B27" t="n">
+        <v>14640</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>14880</v>
+      </c>
+      <c r="B28" t="n">
+        <v>15840</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>16020</v>
+      </c>
+      <c r="B29" t="n">
+        <v>16080</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>16320</v>
+      </c>
+      <c r="B30" t="n">
+        <v>17280</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
